--- a/process/2 - architectural analysis/Requirements.xlsx
+++ b/process/2 - architectural analysis/Requirements.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julfrat\Workspace\study-sra\process\2 - architectural analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joaquim.motger\Projectes\study-sra\process\2 - architectural analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61D2A58E-8489-4356-BE25-1AF75D8AA7BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FF2C400-3BF9-43BB-9D4A-1DFC80C7781A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-10780" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="System" sheetId="1" r:id="rId1"/>
-    <sheet name="Architecture" sheetId="2" r:id="rId2"/>
-    <sheet name="References" sheetId="3" r:id="rId3"/>
+    <sheet name="References" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -58,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="173">
   <si>
     <t>ID</t>
   </si>
@@ -82,9 +84,6 @@
   </si>
   <si>
     <t>Locator</t>
-  </si>
-  <si>
-    <t>Comment</t>
   </si>
   <si>
     <t>SR01</t>
@@ -557,252 +556,6 @@
   </si>
   <si>
     <t xml:space="preserve"> [3]; [4]; [5]</t>
-  </si>
-  <si>
-    <t>Domain Concepts</t>
-  </si>
-  <si>
-    <t>AR1</t>
-  </si>
-  <si>
-    <t>The reference architecture of NLP4RE tools shall prescribe a common architecture consisting of standalone, reusable modules with a black-box interface.</t>
-  </si>
-  <si>
-    <t>A modular architecture with standalone, reusable components and black-box interfaces promotes maintainability, interoperability, and reuse across NLP4RE tools.</t>
-  </si>
-  <si>
-    <t>SR10, SR11, SR07, SR33</t>
-  </si>
-  <si>
-    <t>Module</t>
-  </si>
-  <si>
-    <t>AR1.1</t>
-  </si>
-  <si>
-    <t>The reference architecture of NLP4RE tools shall contain an input module that consumes software artifacts in various data formats and produces an output for a pre-processing module.</t>
-  </si>
-  <si>
-    <t>An input module capable of handling diverse data formats enables flexibility and integration with multiple RE data sources.</t>
-  </si>
-  <si>
-    <t>SR10, SR11, SR07</t>
-  </si>
-  <si>
-    <t>Input Consumer</t>
-  </si>
-  <si>
-    <t>AR1.2</t>
-  </si>
-  <si>
-    <t>The reference architecture of NLP4RE tools shall contain a pre-processing module that consumes the output of an input module, pre-processes the input software artifacts, and produces an output for a processing module.</t>
-  </si>
-  <si>
-    <t>A pre-processing module standardizes and cleans input artifacts, ensuring that subsequent processing stages operate on consistent, structured data.</t>
-  </si>
-  <si>
-    <t>Pre-Processor</t>
-  </si>
-  <si>
-    <t>The reference architecture shall contain a [MODULE NAME] module that consumes the output of an [INPUT MODULE], [ACTION] the [INPUT MODULE], and produces an output for a [OUTPUT MODULE].</t>
-  </si>
-  <si>
-    <t>AR1.3</t>
-  </si>
-  <si>
-    <t>The reference architecture of NLP4RE tools shall contain a processing module that consumes the output of a pre-processing module, processes the pre-processed input, and produces an output for a post-processing module.</t>
-  </si>
-  <si>
-    <t>A dedicated processing module encapsulates the core NLP functionality, enabling clear separation of concerns and focused algorithmic development.</t>
-  </si>
-  <si>
-    <t>Processor</t>
-  </si>
-  <si>
-    <t>AR1.4</t>
-  </si>
-  <si>
-    <t>The reference architecture of NLP4RE tools shall contain a post-processing module that consumes the output of a processing module, post-processes the processed input, and produces an output for an output module.</t>
-  </si>
-  <si>
-    <t>A post-processing module transforms and refines processed outputs to ensure they are interpretable and suitable for presentation or evaluation.</t>
-  </si>
-  <si>
-    <t>Post-Processor</t>
-  </si>
-  <si>
-    <t>AR1.4.1</t>
-  </si>
-  <si>
-    <t>The post-processing module shall provide an interface to a evaluation system.</t>
-  </si>
-  <si>
-    <t>Providing an evaluation interface supports benchmarking, comparability, and reproducibility of tool performance.</t>
-  </si>
-  <si>
-    <t>Benchmark</t>
-  </si>
-  <si>
-    <t>AR1.5</t>
-  </si>
-  <si>
-    <t>The reference architecture of NLP4RE tools shall contain a output module that consumes the output of a post-processing module, formats this artifact, and visualizes them in a user interface.</t>
-  </si>
-  <si>
-    <t>An output module that formats and visualizes results improves usability and facilitates interpretation by end users.</t>
-  </si>
-  <si>
-    <t>SR10, SR11, SR07, SR36</t>
-  </si>
-  <si>
-    <t>Output Producer</t>
-  </si>
-  <si>
-    <t>AR1.6</t>
-  </si>
-  <si>
-    <t>Every module in the reference architecture of NLP4RE tools should preserve every execution (consisting of the input, output, and all auxiliary information) in a secure manner.</t>
-  </si>
-  <si>
-    <t>Securely storing all executions, including inputs, outputs, and metadata, ensures data integrity, reproducibility, and compliance with privacy requirements.</t>
-  </si>
-  <si>
-    <t>SR15, SR09</t>
-  </si>
-  <si>
-    <t>Storage System</t>
-  </si>
-  <si>
-    <t>AR2</t>
-  </si>
-  <si>
-    <t>The reference architecture of NLP4RE tools shall enforce that every high-level component of a tool explains the syntax and limitations to its input (including the language of NL-based artifacts) and output (including bias of generative models).</t>
-  </si>
-  <si>
-    <t>Explicitly documenting input and output syntax, limitations, and potential biases enhances transparency, trust, and responsible model use.</t>
-  </si>
-  <si>
-    <t>SR21, SR22, SR25, SR05</t>
-  </si>
-  <si>
-    <t>Module::io_syntax_limitations</t>
-  </si>
-  <si>
-    <t>SR5 -&gt; documenting language limitations</t>
-  </si>
-  <si>
-    <t>AR3</t>
-  </si>
-  <si>
-    <t>The reference architecture of NLP4RE tools shall enforce that both the overall tool and all of its high-level components explain the output and its relationship to the input.</t>
-  </si>
-  <si>
-    <t>Linking each output to its corresponding input improves interpretability, validation, and traceability throughout RE analyses.</t>
-  </si>
-  <si>
-    <t>SR06, SR37, SR13</t>
-  </si>
-  <si>
-    <t>Product::confidence; Product::explanation</t>
-  </si>
-  <si>
-    <t>AR4</t>
-  </si>
-  <si>
-    <t>The reference architecture of NLP4RE tools should facilitate the consumption and production of different data formats of input and output artifact.</t>
-  </si>
-  <si>
-    <t>Supporting multiple input and output data formats ensures interoperability and integration with diverse tools and workflows.</t>
-  </si>
-  <si>
-    <t>SR02, SR38</t>
-  </si>
-  <si>
-    <t>Input Artifact; Product</t>
-  </si>
-  <si>
-    <t>AR5</t>
-  </si>
-  <si>
-    <t>The reference architecture of NLP4RE tools should enforce that the accepted language of the input artifacts is a configurable parameter.</t>
-  </si>
-  <si>
-    <t>Configurable language parameters enable multilingual applicability and adaptability across RE contexts.</t>
-  </si>
-  <si>
-    <t>Language</t>
-  </si>
-  <si>
-    <t>AR6</t>
-  </si>
-  <si>
-    <t>The reference architecture of NLP4RE tools should enforce that any tool is documented according to a common standard.</t>
-  </si>
-  <si>
-    <t>Standardized documentation ensures consistent understanding, maintenance, and evolution of NLP4RE tools.</t>
-  </si>
-  <si>
-    <t>Documentation; NLP4RE ID Card</t>
-  </si>
-  <si>
-    <t>Check tool / module</t>
-  </si>
-  <si>
-    <t>AR6.1</t>
-  </si>
-  <si>
-    <t>The reference architecture of NLP4RE tools should enforce that the documentation of a tool should uniquely identify its version and the version of all the modules it uses.</t>
-  </si>
-  <si>
-    <t>Including version identifiers for both the tool and its modules supports reproducibility and controlled evolution.</t>
-  </si>
-  <si>
-    <t>Tool Version; Module::version</t>
-  </si>
-  <si>
-    <t>Make clear that this is only one important aspect</t>
-  </si>
-  <si>
-    <t>AR6.2</t>
-  </si>
-  <si>
-    <t>The reference architecture of NLP4RE tools should enforce that the documentation of a tool should specify a unique name and contain a comprehensive tool description covering the NLP techniques, NLP task, and RE task, as well as the input and output artifacts it processes.</t>
-  </si>
-  <si>
-    <t>Comprehensive documentation describing the tool’s name, purpose, NLP and RE tasks, and processed artifacts ensures clarity and comparability across implementations.</t>
-  </si>
-  <si>
-    <t>SR29, SR32</t>
-  </si>
-  <si>
-    <t>Tool; Documentation; Name; Description; NLP Technology; NLP Task; RE Task</t>
-  </si>
-  <si>
-    <t>AR6.3</t>
-  </si>
-  <si>
-    <t>The reference architecture of NLP4RE tools should enforce that the documentation of a tool or module specifies all dependencies and their versions.</t>
-  </si>
-  <si>
-    <t>Listing all dependencies and their versions prevents incompatibilities and facilitates long-term maintainability.</t>
-  </si>
-  <si>
-    <t>Dependency</t>
-  </si>
-  <si>
-    <t>AR7</t>
-  </si>
-  <si>
-    <t>The reference architecture of NLP4RE tools shall encourage that all source material of a tool are available long-term online and under an open-source license.</t>
-  </si>
-  <si>
-    <t>Releasing source materials online under open-source licenses ensures accessibility, long-term preservation, and collaborative advancement of NLP4RE tools.</t>
-  </si>
-  <si>
-    <t>SR30, SR31</t>
-  </si>
-  <si>
-    <t>Source Code; License</t>
   </si>
   <si>
     <t>Reference</t>
@@ -1210,973 +963,973 @@
     </row>
     <row r="2" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>16</v>
       </c>
       <c r="I2" s="4"/>
     </row>
     <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>28</v>
       </c>
       <c r="I4" s="4"/>
     </row>
     <row r="5" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>33</v>
       </c>
       <c r="I5" s="4"/>
     </row>
     <row r="6" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="G6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>33</v>
       </c>
       <c r="I6" s="4"/>
     </row>
     <row r="7" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="I8" s="4"/>
     </row>
     <row r="9" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>55</v>
       </c>
       <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="G11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>60</v>
       </c>
       <c r="I11" s="4"/>
     </row>
     <row r="12" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="G12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>65</v>
       </c>
       <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" s="4" t="s">
+      <c r="F13" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="G13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>69</v>
       </c>
       <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="4" t="s">
+      <c r="F14" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="G14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>73</v>
       </c>
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="F15" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="G15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>78</v>
       </c>
       <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E16" s="4" t="s">
+      <c r="F16" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>81</v>
-      </c>
       <c r="G16" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17" s="4" t="s">
+      <c r="F17" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="G17" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>84</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>85</v>
       </c>
       <c r="I17" s="4"/>
     </row>
     <row r="18" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" s="4" t="s">
+      <c r="F18" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="G18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E19" s="4" t="s">
+      <c r="F19" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="G19" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>93</v>
       </c>
       <c r="I19" s="4"/>
     </row>
     <row r="20" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E20" s="4" t="s">
+      <c r="F20" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="G20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>97</v>
       </c>
       <c r="I20" s="4"/>
     </row>
     <row r="21" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="F21" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="G21" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>102</v>
       </c>
       <c r="I21" s="4"/>
     </row>
     <row r="22" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="4" t="s">
+      <c r="F22" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="G22" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>106</v>
       </c>
       <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E23" s="4" t="s">
+      <c r="F23" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="G23" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H23" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>110</v>
       </c>
       <c r="I23" s="4"/>
     </row>
     <row r="24" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="F24" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="G24" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>115</v>
       </c>
       <c r="I24" s="4"/>
     </row>
     <row r="25" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E25" s="4" t="s">
+      <c r="F25" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="G25" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>119</v>
       </c>
       <c r="I25" s="4"/>
     </row>
     <row r="26" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E26" s="4" t="s">
+      <c r="F26" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="F26" s="4" t="s">
-        <v>122</v>
-      </c>
       <c r="G26" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I26" s="4"/>
     </row>
     <row r="27" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="C27" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27" s="7" t="s">
+      <c r="F27" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="G27" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G27" s="7" t="s">
+      <c r="H27" s="7" t="s">
         <v>127</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>128</v>
       </c>
       <c r="I27" s="7"/>
     </row>
     <row r="28" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28" s="7" t="s">
+      <c r="F28" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="G28" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H28" s="7" t="s">
         <v>131</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>132</v>
       </c>
       <c r="I28" s="7"/>
     </row>
     <row r="29" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E29" s="7" t="s">
+      <c r="F29" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="G29" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H29" s="7" t="s">
         <v>135</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>136</v>
       </c>
       <c r="I29" s="7"/>
     </row>
     <row r="30" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="4" t="s">
+      <c r="F30" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="G30" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="H30" s="4" t="s">
         <v>139</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>140</v>
       </c>
       <c r="I30" s="4"/>
     </row>
     <row r="31" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E31" s="4" t="s">
+      <c r="F31" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="G31" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="H31" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>144</v>
       </c>
       <c r="I31" s="4"/>
     </row>
     <row r="32" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E32" s="4" t="s">
+      <c r="F32" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>147</v>
-      </c>
       <c r="G32" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I32" s="4"/>
     </row>
     <row r="33" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E33" s="4" t="s">
+      <c r="F33" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="F33" s="4" t="s">
-        <v>150</v>
-      </c>
       <c r="G33" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I33" s="4"/>
     </row>
     <row r="34" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E34" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E34" s="4" t="s">
+      <c r="F34" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="G34" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="H34" s="4" t="s">
         <v>153</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>154</v>
       </c>
       <c r="I34" s="4"/>
     </row>
     <row r="35" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E35" s="4" t="s">
+      <c r="F35" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="G35" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="H35" s="4" t="s">
         <v>157</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>158</v>
       </c>
       <c r="I35" s="4"/>
     </row>
     <row r="36" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E36" s="4" t="s">
+      <c r="F36" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="F36" s="4" t="s">
-        <v>161</v>
-      </c>
       <c r="G36" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I36" s="4"/>
     </row>
     <row r="37" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E37" s="4" t="s">
+      <c r="F37" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="G37" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H37" s="4" t="s">
         <v>164</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>165</v>
       </c>
       <c r="I37" s="4"/>
     </row>
@@ -2202,433 +1955,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="10.21875" customWidth="1"/>
-    <col min="3" max="3" width="65.21875" style="9" customWidth="1"/>
-    <col min="4" max="4" width="59.88671875" style="9" customWidth="1"/>
-    <col min="5" max="5" width="19.88671875" style="9" customWidth="1"/>
-    <col min="6" max="6" width="39.33203125" style="9" customWidth="1"/>
-    <col min="7" max="7" width="59.109375" hidden="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="G2" s="4"/>
-    </row>
-    <row r="3" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="G3" s="4"/>
-    </row>
-    <row r="4" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="G5" s="4"/>
-    </row>
-    <row r="6" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="G7" s="4"/>
-    </row>
-    <row r="8" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="G8" s="4"/>
-    </row>
-    <row r="9" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="G9" s="4"/>
-    </row>
-    <row r="10" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="G11" s="4"/>
-    </row>
-    <row r="12" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="G12" s="4"/>
-    </row>
-    <row r="13" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="G13" s="4"/>
-    </row>
-    <row r="14" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="G16" s="4"/>
-    </row>
-    <row r="17" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="G17" s="4"/>
-    </row>
-    <row r="18" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="G18" s="4"/>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B18" xr:uid="{00000000-0002-0000-0100-000001000000}">
-      <formula1>"FR,NFR"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
-          <x14:formula1>
-            <xm:f>System!$A$2:$A18</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E18</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -2645,47 +1971,47 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>248</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>249</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>250</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="92.4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>251</v>
+        <v>168</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>252</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>253</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>254</v>
+        <v>171</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>255</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
